--- a/data/trans_orig/P64B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P64B-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>19215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39021</t>
+          <t>39907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67476</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>22056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51273</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44577</t>
+          <t>47260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>60089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90317</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>79304</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105998</t>
+          <t>105712</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>73266</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135629</t>
+          <t>135955</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170738</t>
+          <t>171957</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>52623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92585</t>
+          <t>91219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130906</t>
+          <t>130596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59271</t>
+          <t>60921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92411</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>161447</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>211147</t>
+          <t>211055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25385</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120396</t>
+          <t>123295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164512</t>
+          <t>164334</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90376</t>
+          <t>89293</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123612</t>
+          <t>124037</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>222438</t>
+          <t>219463</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>275069</t>
+          <t>273265</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213907</t>
+          <t>216029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>263140</t>
+          <t>261623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102606</t>
+          <t>101979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138219</t>
+          <t>137572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>328072</t>
+          <t>324991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386258</t>
+          <t>387595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61805</t>
+          <t>62655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50964</t>
+          <t>52448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>83799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77700</t>
+          <t>76715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113495</t>
+          <t>115956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78510</t>
+          <t>79464</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>137193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184052</t>
+          <t>183924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26251</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142650</t>
+          <t>141656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188410</t>
+          <t>184341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97498</t>
+          <t>97128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130914</t>
+          <t>131187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248827</t>
+          <t>250758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304980</t>
+          <t>305456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216549</t>
+          <t>216579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262495</t>
+          <t>263779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66371</t>
+          <t>66485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>97275</t>
+          <t>96700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>289949</t>
+          <t>291181</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>347079</t>
+          <t>351782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>32919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49409</t>
+          <t>49357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57865</t>
+          <t>58158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90250</t>
+          <t>90282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>76492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114750</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100836</t>
+          <t>99899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138952</t>
+          <t>140503</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>57253</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>85706</t>
+          <t>82897</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>166553</t>
+          <t>165746</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>215759</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>179325</t>
+          <t>179726</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>220829</t>
+          <t>222592</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42779</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67649</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>229194</t>
+          <t>231392</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>280694</t>
+          <t>280248</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>36982</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>52811</t>
+          <t>52157</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58481</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>63248</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>91698</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52513</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78298</t>
+          <t>78946</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>68528</t>
+          <t>68315</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>99850</t>
+          <t>97804</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -6297,12 +6297,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>95834</t>
+          <t>94229</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>138898</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6332,12 +6332,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>69322</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6367,12 +6367,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>143924</t>
+          <t>141451</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>195175</t>
+          <t>194412</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>302648</t>
+          <t>303251</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>372848</t>
+          <t>367260</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>172749</t>
+          <t>172207</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>220258</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>489913</t>
+          <t>487395</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>576143</t>
+          <t>572085</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -6523,12 +6523,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>51991</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>36718</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>65909</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6636,12 +6636,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>50994</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>118041</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>471677</t>
+          <t>472391</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>551550</t>
+          <t>552222</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>327297</t>
+          <t>325894</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>392476</t>
+          <t>386996</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>817992</t>
+          <t>818615</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>922726</t>
+          <t>925255</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -6862,12 +6862,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>789797</t>
+          <t>791207</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>879145</t>
+          <t>879699</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>302321</t>
+          <t>303123</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>363157</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1118914</t>
+          <t>1117450</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1223211</t>
+          <t>1224374</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28754</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22218</t>
+          <t>21998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>49720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52683</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>80030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -8122,12 +8122,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8137,12 +8137,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25135</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -8235,12 +8235,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61788</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94023</t>
+          <t>95085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61683</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105534</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146744</t>
+          <t>145837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -8348,12 +8348,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39346</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -8574,12 +8574,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71055</t>
+          <t>70875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103787</t>
+          <t>103582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86693</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121924</t>
+          <t>120222</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>166423</t>
+          <t>168432</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>214086</t>
+          <t>216190</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -8687,12 +8687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146329</t>
+          <t>143605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183172</t>
+          <t>184563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73389</t>
+          <t>70110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103625</t>
+          <t>102725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225801</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>278381</t>
+          <t>277816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>66974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -9030,12 +9030,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93554</t>
+          <t>94221</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131175</t>
+          <t>132195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33204</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59548</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135044</t>
+          <t>131259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>180110</t>
+          <t>178391</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -9143,12 +9143,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20537</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -9256,12 +9256,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40972</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -9369,12 +9369,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>90536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129665</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90483</t>
+          <t>90639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125021</t>
+          <t>123407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190509</t>
+          <t>190356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240930</t>
+          <t>240739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -9482,12 +9482,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129929</t>
+          <t>130187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>169230</t>
+          <t>170871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74733</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107368</t>
+          <t>107762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215637</t>
+          <t>212694</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>264688</t>
+          <t>266304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -9712,12 +9712,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>25661</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53070</t>
+          <t>51768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72831</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107926</t>
+          <t>108114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>41426</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98896</t>
+          <t>98488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144306</t>
+          <t>141262</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -9938,12 +9938,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35936</t>
+          <t>36945</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>105755</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>143317</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74466</t>
+          <t>76047</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107136</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>187365</t>
+          <t>191330</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>238463</t>
+          <t>242103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10249,12 +10249,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -10277,12 +10277,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104685</t>
+          <t>103564</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143892</t>
+          <t>142928</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45406</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74814</t>
+          <t>74760</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10347,12 +10347,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157916</t>
+          <t>160743</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>206605</t>
+          <t>206994</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -10620,12 +10620,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>40343</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -10655,12 +10655,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>31367</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55759</t>
+          <t>56110</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -10881,12 +10881,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10916,12 +10916,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -10959,12 +10959,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>28393</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -11029,12 +11029,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>76795</t>
+          <t>76298</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -11072,12 +11072,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>54287</t>
+          <t>55859</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>79213</t>
+          <t>80166</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>32451</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>76559</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>106518</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -12892,12 +12892,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>58515</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>96707</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>52854</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>83976</t>
+          <t>84968</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>119438</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>299810</t>
+          <t>299968</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>366852</t>
+          <t>366867</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>127067</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>173888</t>
+          <t>173185</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>441480</t>
+          <t>437395</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>525221</t>
+          <t>526131</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -13118,12 +13118,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>60175</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13133,49 +13133,49 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>11476</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>20841</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>50</t>
@@ -13188,12 +13188,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -13231,12 +13231,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>87301</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>76384</t>
+          <t>76748</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>117703</t>
+          <t>118006</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -13344,12 +13344,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>340594</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>405357</t>
+          <t>408218</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13359,12 +13359,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>315662</t>
+          <t>315312</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>377319</t>
+          <t>375967</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>678490</t>
+          <t>677740</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>768631</t>
+          <t>767122</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -13457,12 +13457,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>494579</t>
+          <t>497830</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>571213</t>
+          <t>571310</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>270507</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>329850</t>
+          <t>327009</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>780944</t>
+          <t>777984</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>877448</t>
+          <t>874497</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -13922,12 +13922,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13937,12 +13937,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13957,12 +13957,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13972,12 +13972,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13992,12 +13992,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35650</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -14007,12 +14007,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -14035,12 +14035,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22958</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -14070,12 +14070,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>24667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -14085,12 +14085,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -14105,12 +14105,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -14120,12 +14120,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -14296,12 +14296,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14311,12 +14311,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -14331,12 +14331,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14346,12 +14346,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14257</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14424,12 +14424,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14444,12 +14444,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>55407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14459,12 +14459,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -14487,12 +14487,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14522,12 +14522,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>64774</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -14717,12 +14717,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39895</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14787,12 +14787,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50379</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79297</t>
+          <t>80177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14802,12 +14802,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -14830,12 +14830,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>54372</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86130</t>
+          <t>84734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14865,12 +14865,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33371</t>
+          <t>33898</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56473</t>
+          <t>57362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14880,12 +14880,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14900,12 +14900,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91947</t>
+          <t>93055</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131013</t>
+          <t>131554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14915,12 +14915,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -14943,12 +14943,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -15013,12 +15013,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19142</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -15056,12 +15056,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48538</t>
+          <t>48088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -15141,12 +15141,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -15169,12 +15169,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63055</t>
+          <t>63675</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93500</t>
+          <t>95412</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15184,12 +15184,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73560</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102637</t>
+          <t>104177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>146469</t>
+          <t>144177</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>188308</t>
+          <t>188471</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -15282,12 +15282,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108138</t>
+          <t>106777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141637</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15297,12 +15297,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65345</t>
+          <t>64923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95437</t>
+          <t>94599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180913</t>
+          <t>179905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228594</t>
+          <t>227124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -15512,12 +15512,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31252</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57411</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15527,12 +15527,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15547,12 +15547,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41848</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15562,12 +15562,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15582,12 +15582,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57150</t>
+          <t>54686</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90913</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15597,12 +15597,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -15625,12 +15625,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>64780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100466</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15640,12 +15640,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15660,12 +15660,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64276</t>
+          <t>63677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109690</t>
+          <t>111204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152750</t>
+          <t>152187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -15738,12 +15738,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -15851,12 +15851,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15866,12 +15866,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15886,12 +15886,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39874</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -15964,12 +15964,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108559</t>
+          <t>107552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>147046</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15999,12 +15999,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91156</t>
+          <t>91293</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123129</t>
+          <t>122555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>206810</t>
+          <t>209245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>259583</t>
+          <t>258999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -16077,12 +16077,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>150327</t>
+          <t>149225</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>191057</t>
+          <t>190461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -16112,12 +16112,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80571</t>
+          <t>79882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110772</t>
+          <t>111794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>238704</t>
+          <t>240118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292755</t>
+          <t>290679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16162,12 +16162,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -16307,12 +16307,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55794</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16322,12 +16322,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45588</t>
+          <t>43510</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55825</t>
+          <t>55494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90275</t>
+          <t>90904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -16420,12 +16420,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42608</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>72672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16435,12 +16435,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>23826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46468</t>
+          <t>46085</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74021</t>
+          <t>75380</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108788</t>
+          <t>111302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -16533,12 +16533,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -16646,12 +16646,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16661,12 +16661,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16681,12 +16681,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29144</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16696,12 +16696,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16716,12 +16716,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>42340</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16731,12 +16731,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -16759,12 +16759,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>82001</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>117801</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16774,12 +16774,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>62211</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91089</t>
+          <t>92080</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16809,12 +16809,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>153235</t>
+          <t>150995</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>200900</t>
+          <t>198530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16844,12 +16844,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -16872,12 +16872,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113657</t>
+          <t>112021</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153199</t>
+          <t>149439</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16887,12 +16887,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16907,12 +16907,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49526</t>
+          <t>50641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77677</t>
+          <t>78612</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16922,12 +16922,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16942,12 +16942,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>171871</t>
+          <t>170826</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219008</t>
+          <t>218117</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16957,12 +16957,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -17102,12 +17102,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -17117,47 +17117,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>14098</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>23630</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
           <t>7,54%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>14098</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>7927</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>23120</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>46608</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -17215,12 +17215,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>42255</t>
+          <t>42329</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17230,12 +17230,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17250,12 +17250,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17285,12 +17285,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>63448</t>
+          <t>62320</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17300,12 +17300,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -17476,12 +17476,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17491,12 +17491,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17511,12 +17511,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -17554,12 +17554,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41399</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>66127</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17569,12 +17569,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17589,12 +17589,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>47271</t>
+          <t>48595</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17609,7 +17609,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17624,12 +17624,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>73981</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>107311</t>
+          <t>106916</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17639,12 +17639,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -17667,12 +17667,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>69077</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17682,12 +17682,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17717,12 +17717,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17737,12 +17737,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>71772</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>102926</t>
+          <t>102468</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -18419,12 +18419,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18434,12 +18434,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -18532,12 +18532,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18547,12 +18547,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -19487,12 +19487,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>125564</t>
+          <t>124040</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>172246</t>
+          <t>172671</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19502,12 +19502,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19522,12 +19522,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>100767</t>
+          <t>99210</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>143257</t>
+          <t>141052</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19537,12 +19537,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>233643</t>
+          <t>237459</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>299563</t>
+          <t>303600</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19572,12 +19572,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>222196</t>
+          <t>224029</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>283537</t>
+          <t>281789</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19615,12 +19615,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19635,12 +19635,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>138871</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>184876</t>
+          <t>186838</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19655,7 +19655,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19670,12 +19670,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>377810</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>453865</t>
+          <t>452885</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19685,12 +19685,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -19713,12 +19713,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19728,12 +19728,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19748,12 +19748,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19783,12 +19783,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19798,12 +19798,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -19826,12 +19826,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19841,12 +19841,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19861,12 +19861,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>91810</t>
+          <t>92895</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19876,12 +19876,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19896,12 +19896,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>84491</t>
+          <t>85621</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>125812</t>
+          <t>127188</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -19939,12 +19939,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>345134</t>
+          <t>346325</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>411814</t>
+          <t>415061</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -19954,12 +19954,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>303707</t>
+          <t>302458</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>362837</t>
+          <t>364510</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -19989,12 +19989,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -20009,12 +20009,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>672496</t>
+          <t>665076</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>763169</t>
+          <t>759358</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -20024,12 +20024,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>478631</t>
+          <t>478852</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>553039</t>
+          <t>551818</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -20067,12 +20067,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -20087,12 +20087,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>267843</t>
+          <t>268576</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>324600</t>
+          <t>326552</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -20102,12 +20102,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>763154</t>
+          <t>764990</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>853926</t>
+          <t>856322</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -20137,12 +20137,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
